--- a/python-excel-acf-pacf-demo.xlsx
+++ b/python-excel-acf-pacf-demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2000001_{7480B3BC-03B3-4786-8D65-6C9D898B353D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCE8D42-DECA-4889-8284-218A9BB0FF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -153,7 +153,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization>
+    <initialization userModified="1">
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -254,10 +254,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="\$0.00"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -301,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -311,6 +312,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -333,15 +335,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>423333</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>169334</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>521819</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>30752</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>118533</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -369,7 +371,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3310467" y="3297767"/>
+          <a:off x="3733800" y="3293534"/>
           <a:ext cx="3929652" cy="2201333"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -381,16 +383,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>677333</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>173566</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>634999</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>80432</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>266699</xdr:colOff>
+      <xdr:colOff>664632</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>24117</xdr:rowOff>
+      <xdr:rowOff>104550</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -418,7 +420,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3310466" y="5727699"/>
+          <a:off x="3945466" y="5808132"/>
           <a:ext cx="3674533" cy="2801185"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -431,15 +433,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>478367</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>110067</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>431302</xdr:colOff>
+      <xdr:colOff>672603</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>140893</xdr:rowOff>
+      <xdr:rowOff>77393</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -467,7 +469,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3310467" y="8851900"/>
+          <a:off x="3788834" y="8788400"/>
           <a:ext cx="5193802" cy="3959360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -933,6 +935,7 @@
     <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2170,20 +2173,20 @@
       <c r="D78" s="5">
         <v>0.20979999999999999</v>
       </c>
-      <c r="F78" t="str" cm="1">
+      <c r="F78" s="7" t="str" cm="1">
         <f t="array" ref="F78:J86">_xlfn._xlws.PY(6,0)</f>
         <v/>
       </c>
-      <c r="G78" t="str">
+      <c r="G78" s="7" t="str">
         <v>coef</v>
       </c>
-      <c r="H78" t="str">
+      <c r="H78" s="7" t="str">
         <v>std_error</v>
       </c>
-      <c r="I78" t="str">
+      <c r="I78" s="7" t="str">
         <v>z</v>
       </c>
-      <c r="J78" t="str">
+      <c r="J78" s="7" t="str">
         <v>p_value</v>
       </c>
     </row>
@@ -2200,19 +2203,19 @@
       <c r="D79" s="5">
         <v>0.23</v>
       </c>
-      <c r="F79" t="str">
+      <c r="F79" s="7" t="str">
         <v>const</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="7">
         <v>0.1949327571836228</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="7">
         <v>3.4662336585612181E-3</v>
       </c>
-      <c r="I79">
+      <c r="I79" s="7">
         <v>56.237627461195586</v>
       </c>
-      <c r="J79">
+      <c r="J79" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2229,19 +2232,19 @@
       <c r="D80" s="5">
         <v>0.18940000000000001</v>
       </c>
-      <c r="F80" t="str">
+      <c r="F80" s="7" t="str">
         <v>ar.L1</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="7">
         <v>0.70075746835623665</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="7">
         <v>0.10121806405900315</v>
       </c>
-      <c r="I80">
+      <c r="I80" s="7">
         <v>6.9232451230023866</v>
       </c>
-      <c r="J80">
+      <c r="J80" s="7">
         <v>4.4141298577131686E-12</v>
       </c>
     </row>
@@ -2258,19 +2261,19 @@
       <c r="D81" s="5">
         <v>0.19650000000000001</v>
       </c>
-      <c r="F81" t="str">
+      <c r="F81" s="7" t="str">
         <v>ma.L1</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="7">
         <v>4.9438500556738081E-3</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="7">
         <v>0.10992739162412687</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="7">
         <v>4.4973777532885E-2</v>
       </c>
-      <c r="J81">
+      <c r="J81" s="7">
         <v>0.9641282102963965</v>
       </c>
     </row>
@@ -2287,19 +2290,19 @@
       <c r="D82" s="5">
         <v>0.20699999999999999</v>
       </c>
-      <c r="F82" t="str">
+      <c r="F82" s="7" t="str">
         <v>ma.L2</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="7">
         <v>4.4904979924042215E-2</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="7">
         <v>8.1751896661309706E-2</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="7">
         <v>0.54928364671561392</v>
       </c>
-      <c r="J82">
+      <c r="J82" s="7">
         <v>0.58281080825334741</v>
       </c>
     </row>
@@ -2316,19 +2319,19 @@
       <c r="D83" s="5">
         <v>0.1996</v>
       </c>
-      <c r="F83" t="str">
+      <c r="F83" s="7" t="str">
         <v>ma.L3</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="7">
         <v>6.238705080614896E-2</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="7">
         <v>6.5623746508454761E-2</v>
       </c>
-      <c r="I83">
+      <c r="I83" s="7">
         <v>0.95067798054034003</v>
       </c>
-      <c r="J83">
+      <c r="J83" s="7">
         <v>0.3417678693679318</v>
       </c>
     </row>
@@ -2345,19 +2348,19 @@
       <c r="D84" s="5">
         <v>0.191</v>
       </c>
-      <c r="F84" t="str">
+      <c r="F84" s="7" t="str">
         <v>ma.L4</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="7">
         <v>6.3493977259320392E-2</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="7">
         <v>5.935015580251099E-2</v>
       </c>
-      <c r="I84">
+      <c r="I84" s="7">
         <v>1.069819891806149</v>
       </c>
-      <c r="J84">
+      <c r="J84" s="7">
         <v>0.28470038680060727</v>
       </c>
     </row>
@@ -2374,19 +2377,19 @@
       <c r="D85" s="5">
         <v>0.2326</v>
       </c>
-      <c r="F85" t="str">
+      <c r="F85" s="7" t="str">
         <v>ma.L5</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="7">
         <v>8.0501379817589064E-2</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="7">
         <v>5.3008488938912843E-2</v>
       </c>
-      <c r="I85">
+      <c r="I85" s="7">
         <v>1.5186507185737574</v>
       </c>
-      <c r="J85">
+      <c r="J85" s="7">
         <v>0.12885043743906763</v>
       </c>
     </row>
@@ -2403,19 +2406,19 @@
       <c r="D86" s="5">
         <v>0.247</v>
       </c>
-      <c r="F86" t="str">
+      <c r="F86" s="7" t="str">
         <v>sigma2</v>
       </c>
-      <c r="G86">
+      <c r="G86" s="7">
         <v>3.5060912991016465E-4</v>
       </c>
-      <c r="H86">
+      <c r="H86" s="7">
         <v>2.1952643797406989E-5</v>
       </c>
-      <c r="I86">
+      <c r="I86" s="7">
         <v>15.971157421666817</v>
       </c>
-      <c r="J86">
+      <c r="J86" s="7">
         <v>2.029840358145676E-57</v>
       </c>
     </row>
@@ -8511,9 +8514,10 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
